--- a/Data/5odamWithRoles.xlsx
+++ b/Data/5odamWithRoles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eng Farid\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\marmina\api\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242555A7-2F5C-4F5C-9598-6976485B6A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBEE401-2D0D-42C3-A6B3-CBB33BDF2CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -1607,10 +1607,12 @@
   <dimension ref="A1:N74"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="18.88671875" customWidth="1"/>
-    <col min="9" max="9" width="24.77734375" customWidth="1"/>
-    <col min="10" max="10" width="27.44140625" customWidth="1"/>
-    <col min="11" max="13" width="18.88671875" customWidth="1"/>
+    <col min="1" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="8" width="18.88671875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="24.77734375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="18.88671875" customWidth="1"/>
     <col min="14" max="14" width="18.88671875" style="9" customWidth="1"/>
     <col min="15" max="18" width="18.88671875" customWidth="1"/>
   </cols>
